--- a/product_selector_out/STM32MP253.xlsx
+++ b/product_selector_out/STM32MP253.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -85,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -98,7 +93,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1184,7 +1178,7 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1455,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1732,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2009,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2538,9 +2532,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2598,7 +2592,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2618,7 +2612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2628,7 +2622,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2643,7 +2637,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2668,12 +2662,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2688,19 +2682,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ12" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK12" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL12" s="6" t="inlineStr">
@@ -2753,7 +2747,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="8" t="inlineStr">
+      <c r="AV12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2763,17 +2757,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2788,9 +2782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -2815,9 +2809,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2875,7 +2869,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2895,7 +2889,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="U13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2915,12 +2909,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2945,12 +2939,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2965,19 +2959,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ13" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK13" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr">
@@ -2995,12 +2989,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP13" s="8" t="inlineStr">
+      <c r="AO13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3030,7 +3024,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3040,17 +3034,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3065,9 +3059,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3092,9 +3086,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3152,7 +3146,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3172,7 +3166,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3192,12 +3186,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3222,12 +3216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3242,19 +3236,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ14" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK14" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr">
@@ -3307,7 +3301,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="8" t="inlineStr">
+      <c r="AV14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3317,17 +3311,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ14" s="8" t="inlineStr">
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3342,9 +3336,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3369,9 +3363,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -3429,7 +3423,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3449,7 +3443,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="U15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3469,12 +3463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3499,12 +3493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3519,19 +3513,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ15" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK15" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL15" s="6" t="inlineStr">
@@ -3549,12 +3543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP15" s="8" t="inlineStr">
+      <c r="AO15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3584,7 +3578,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV15" s="8" t="inlineStr">
+      <c r="AV15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3594,17 +3588,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3619,9 +3613,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3671,270 +3665,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32MP253.xlsx
+++ b/product_selector_out/STM32MP253.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -93,6 +98,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1178,7 +1184,7 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1461,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1738,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2015,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -2532,9 +2538,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2592,7 +2598,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2612,7 +2618,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2622,7 +2628,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2637,7 +2643,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2662,12 +2668,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2682,19 +2688,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ12" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK12" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL12" s="6" t="inlineStr">
@@ -2747,7 +2753,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="7" t="inlineStr">
+      <c r="AV12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2757,17 +2763,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ12" s="7" t="inlineStr">
+      <c r="AX12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2782,9 +2788,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -2809,9 +2815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2869,7 +2875,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2889,7 +2895,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="7" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2909,12 +2915,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2939,12 +2945,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2959,19 +2965,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ13" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK13" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr">
@@ -2989,12 +2995,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP13" s="7" t="inlineStr">
+      <c r="AO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3024,7 +3030,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="7" t="inlineStr">
+      <c r="AV13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3034,17 +3040,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ13" s="7" t="inlineStr">
+      <c r="AX13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3059,9 +3065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3086,9 +3092,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3146,7 +3152,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3166,7 +3172,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="7" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3186,12 +3192,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3216,12 +3222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3236,19 +3242,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ14" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK14" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr">
@@ -3301,7 +3307,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="7" t="inlineStr">
+      <c r="AV14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3311,17 +3317,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ14" s="7" t="inlineStr">
+      <c r="AX14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3336,9 +3342,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3363,9 +3369,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -3423,7 +3429,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3443,7 +3449,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="7" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3463,12 +3469,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3493,12 +3499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3513,19 +3519,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ15" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK15" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL15" s="6" t="inlineStr">
@@ -3543,12 +3549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP15" s="7" t="inlineStr">
+      <c r="AO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3578,7 +3584,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV15" s="7" t="inlineStr">
+      <c r="AV15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3588,17 +3594,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ15" s="7" t="inlineStr">
+      <c r="AX15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3613,9 +3619,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3665,7 +3671,270 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32MP253.xlsx
+++ b/product_selector_out/STM32MP253.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC15"/>
+  <dimension ref="A1:BD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.828125" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,8 @@
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
     <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="52" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="52" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -827,6 +828,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -904,6 +910,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1181,6 +1188,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1458,6 +1470,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1735,6 +1752,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2012,9 +2034,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="56">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2027,16 +2054,18 @@
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="M10:M11"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AJ10:AJ11"/>
-    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AP10:AP11"/>
-    <mergeCell ref="BA10:BA11"/>
-    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="AK10:AK11"/>
@@ -2048,9 +2077,8 @@
     <mergeCell ref="Z10:Z11"/>
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
-    <mergeCell ref="A1:BC8"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A9:BC9"/>
+    <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="AE10:AF10"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
@@ -2088,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC15"/>
+  <dimension ref="A1:BD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2146,6 +2174,7 @@
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
     <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2433,6 +2462,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -2510,6 +2544,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2787,6 +2822,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3064,6 +3104,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3341,6 +3386,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3618,11 +3668,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BC9"/>
-    <mergeCell ref="A1:BC8"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
